--- a/Commissioning_Monthly_Review_Tool.xlsx
+++ b/Commissioning_Monthly_Review_Tool.xlsx
@@ -36,6 +36,10 @@
     <definedName name="LIST_ORG">'08_Lists_Config'!$Q$6:$Q$9</definedName>
     <definedName name="LIST_APPROVED">'08_Lists_Config'!$R$6:$R$9</definedName>
     <definedName name="LIST_MILESTONE_STATUS">'08_Lists_Config'!$S$6:$S$10</definedName>
+    <definedName name="NAME_TOPIC_IDS">Topic_Register[Topic ID]</definedName>
+    <definedName name="NAME_ACTION_IDS">Action_Register[Action ID]</definedName>
+    <definedName name="NAME_PQCP_STEPS">PQCP_Follow_Up[PQCP Step]</definedName>
+    <definedName name="NAME_EVIDENCE_IDS">Document_Evidence[Evidence ID]</definedName>
     <definedName name="DUE_SOON_DAYS">'08_Lists_Config'!$C$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4645,7 +4649,7 @@
     </row>
     <row r="8">
       <c r="B8" s="17">
-        <f>IF([@[Topic]]="","","T"&amp;TEXT(ROW()-7,"000"))</f>
+        <f>IF($I8="","","T"&amp;TEXT(ROW()-7,"000"))</f>
         <v/>
       </c>
       <c r="C8" s="26" t="inlineStr">
@@ -4704,11 +4708,11 @@
         </is>
       </c>
       <c r="N8" s="18">
-        <f t="array" ref="N8">IF([@[Topic ID]]="","",IF(IFERROR(MAX(IF(Update_History[Topic ID]=[@[Topic ID]],ROW(Update_History[Topic ID])-7)),0)=0,"",INDEX(Update_History[Meeting Date],IFERROR(MAX(IF(Update_History[Topic ID]=[@[Topic ID]],ROW(Update_History[Topic ID])-7)),0))))</f>
+        <f t="array" ref="N8">IF($B8="","",IF(IFERROR(MAX(IF(Update_History[Topic ID]=$B8,ROW(Update_History[Topic ID])-7)),0)=0,"",INDEX(Update_History[Meeting Date],IFERROR(MAX(IF(Update_History[Topic ID]=$B8,ROW(Update_History[Topic ID])-7)),0))))</f>
         <v/>
       </c>
       <c r="O8" s="17">
-        <f t="array" ref="O8">IF([@[Topic ID]]="","",IF(IFERROR(MAX(IF(Update_History[Topic ID]=[@[Topic ID]],ROW(Update_History[Topic ID])-7)),0)=0,"",INDEX(Update_History[Update / Discussion],IFERROR(MAX(IF(Update_History[Topic ID]=[@[Topic ID]],ROW(Update_History[Topic ID])-7)),0))))</f>
+        <f t="array" ref="O8">IF($B8="","",IF(IFERROR(MAX(IF(Update_History[Topic ID]=$B8,ROW(Update_History[Topic ID])-7)),0)=0,"",INDEX(Update_History[Update / Discussion],IFERROR(MAX(IF(Update_History[Topic ID]=$B8,ROW(Update_History[Topic ID])-7)),0))))</f>
         <v/>
       </c>
       <c r="P8" s="26" t="inlineStr">
@@ -4790,7 +4794,7 @@
         </is>
       </c>
       <c r="AF8" s="49">
-        <f>IF([@[Topic ID]]="",0,IF(OR([@[Discuss at Next Meeting?]]="Yes",[@[Outstanding Point / Gap]]&lt;&gt;"",[@[Question / Decision Required]]&lt;&gt;"",[@[Commissioning Blocker?]]="Yes",[@[Escalation Required?]]="Yes",[@[PQCP Follow-Up Required?]]="Yes",COUNTIFS(Action_Register[Topic ID],[@[Topic ID]],Action_Register[Overdue?],"Yes")&gt;0),1,0))</f>
+        <f>IF($B8="",0,IF(OR($T8="Yes",$L8&lt;&gt;"",$M8&lt;&gt;"",$U8="Yes",$Y8="Yes",$AC8="Yes",COUNTIFS(Action_Register[Topic ID],$B8,Action_Register[Overdue?],"Yes")&gt;0),1,0))</f>
         <v/>
       </c>
       <c r="AG8" s="49">
@@ -4800,7 +4804,7 @@
     </row>
     <row r="9">
       <c r="B9" s="17">
-        <f>IF([@[Topic]]="","","T"&amp;TEXT(ROW()-7,"000"))</f>
+        <f>IF($I9="","","T"&amp;TEXT(ROW()-7,"000"))</f>
         <v/>
       </c>
       <c r="C9" s="26" t="inlineStr">
@@ -4851,11 +4855,11 @@
       <c r="L9" s="26" t="inlineStr"/>
       <c r="M9" s="26" t="inlineStr"/>
       <c r="N9" s="18">
-        <f t="array" ref="N9">IF([@[Topic ID]]="","",IF(IFERROR(MAX(IF(Update_History[Topic ID]=[@[Topic ID]],ROW(Update_History[Topic ID])-7)),0)=0,"",INDEX(Update_History[Meeting Date],IFERROR(MAX(IF(Update_History[Topic ID]=[@[Topic ID]],ROW(Update_History[Topic ID])-7)),0))))</f>
+        <f t="array" ref="N9">IF($B9="","",IF(IFERROR(MAX(IF(Update_History[Topic ID]=$B9,ROW(Update_History[Topic ID])-7)),0)=0,"",INDEX(Update_History[Meeting Date],IFERROR(MAX(IF(Update_History[Topic ID]=$B9,ROW(Update_History[Topic ID])-7)),0))))</f>
         <v/>
       </c>
       <c r="O9" s="17">
-        <f t="array" ref="O9">IF([@[Topic ID]]="","",IF(IFERROR(MAX(IF(Update_History[Topic ID]=[@[Topic ID]],ROW(Update_History[Topic ID])-7)),0)=0,"",INDEX(Update_History[Update / Discussion],IFERROR(MAX(IF(Update_History[Topic ID]=[@[Topic ID]],ROW(Update_History[Topic ID])-7)),0))))</f>
+        <f t="array" ref="O9">IF($B9="","",IF(IFERROR(MAX(IF(Update_History[Topic ID]=$B9,ROW(Update_History[Topic ID])-7)),0)=0,"",INDEX(Update_History[Update / Discussion],IFERROR(MAX(IF(Update_History[Topic ID]=$B9,ROW(Update_History[Topic ID])-7)),0))))</f>
         <v/>
       </c>
       <c r="P9" s="26" t="inlineStr">
@@ -4919,7 +4923,7 @@
         </is>
       </c>
       <c r="AF9" s="49">
-        <f>IF([@[Topic ID]]="",0,IF(OR([@[Discuss at Next Meeting?]]="Yes",[@[Outstanding Point / Gap]]&lt;&gt;"",[@[Question / Decision Required]]&lt;&gt;"",[@[Commissioning Blocker?]]="Yes",[@[Escalation Required?]]="Yes",[@[PQCP Follow-Up Required?]]="Yes",COUNTIFS(Action_Register[Topic ID],[@[Topic ID]],Action_Register[Overdue?],"Yes")&gt;0),1,0))</f>
+        <f>IF($B9="",0,IF(OR($T9="Yes",$L9&lt;&gt;"",$M9&lt;&gt;"",$U9="Yes",$Y9="Yes",$AC9="Yes",COUNTIFS(Action_Register[Topic ID],$B9,Action_Register[Overdue?],"Yes")&gt;0),1,0))</f>
         <v/>
       </c>
       <c r="AG9" s="49">
@@ -5287,7 +5291,7 @@
     </row>
     <row r="8">
       <c r="B8" s="17">
-        <f>IF([@[Action Description]]="","","A"&amp;TEXT(ROW()-7,"000"))</f>
+        <f>IF($D8="","","A"&amp;TEXT(ROW()-7,"000"))</f>
         <v/>
       </c>
       <c r="C8" s="26" t="inlineStr">
@@ -5327,19 +5331,19 @@
         </is>
       </c>
       <c r="K8" s="17">
-        <f>IF([@[Action Description]]="","",IF([@[Closure Date]]&lt;&gt;"",[@[Closure Date]]-[@[Date Raised]],TODAY()-[@[Date Raised]]))</f>
+        <f>IF($D8="","",IF($U8&lt;&gt;"",$U8-$G8,TODAY()-$G8))</f>
         <v/>
       </c>
       <c r="L8" s="17">
-        <f>IF(OR([@[Action Description]]="",[@[Due Date]]=""),"",[@[Due Date]]-TODAY())</f>
+        <f>IF(OR($D8="",$H8=""),"",$H8-TODAY())</f>
         <v/>
       </c>
       <c r="M8" s="17">
-        <f>IF([@[Action Description]]="","",IF(AND([@[Status]]&lt;&gt;"Closed",[@[Status]]&lt;&gt;"Cancelled",[@[Due Date]]&lt;&gt;"",[@[Due Date]]&lt;TODAY()),"Yes","No"))</f>
+        <f>IF($D8="","",IF(AND($I8&lt;&gt;"Closed",$I8&lt;&gt;"Cancelled",$H8&lt;&gt;"",$H8&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
       <c r="N8" s="17">
-        <f t="array" ref="N8">IF([@[Action Description]]="","",IF(IFERROR(MAX(IF(Update_History[Action ID]=[@[Action ID]],ROW(Update_History[Action ID])-7)),0)=0,"",INDEX(Update_History[Update / Discussion],IFERROR(MAX(IF(Update_History[Action ID]=[@[Action ID]],ROW(Update_History[Action ID])-7)),0))))</f>
+        <f t="array" ref="N8">IF($D8="","",IF(IFERROR(MAX(IF(Update_History[Action ID]=$B8,ROW(Update_History[Action ID])-7)),0)=0,"",INDEX(Update_History[Update / Discussion],IFERROR(MAX(IF(Update_History[Action ID]=$B8,ROW(Update_History[Action ID])-7)),0))))</f>
         <v/>
       </c>
       <c r="O8" s="26" t="inlineStr">
@@ -5374,7 +5378,7 @@
       <c r="V8" s="26" t="inlineStr"/>
       <c r="W8" s="26" t="inlineStr"/>
       <c r="X8" s="49">
-        <f>IF([@[Action Description]]="",0,IF(OR([@[Overdue?]]="Yes",[@[Priority]]="Critical"),1,0))</f>
+        <f>IF($D8="",0,IF(OR($M8="Yes",$J8="Critical"),1,0))</f>
         <v/>
       </c>
       <c r="Y8" s="49">
@@ -5384,7 +5388,7 @@
     </row>
     <row r="9">
       <c r="B9" s="17">
-        <f>IF([@[Action Description]]="","","A"&amp;TEXT(ROW()-7,"000"))</f>
+        <f>IF($D9="","","A"&amp;TEXT(ROW()-7,"000"))</f>
         <v/>
       </c>
       <c r="C9" s="26" t="inlineStr">
@@ -5424,19 +5428,19 @@
         </is>
       </c>
       <c r="K9" s="17">
-        <f>IF([@[Action Description]]="","",IF([@[Closure Date]]&lt;&gt;"",[@[Closure Date]]-[@[Date Raised]],TODAY()-[@[Date Raised]]))</f>
+        <f>IF($D9="","",IF($U9&lt;&gt;"",$U9-$G9,TODAY()-$G9))</f>
         <v/>
       </c>
       <c r="L9" s="17">
-        <f>IF(OR([@[Action Description]]="",[@[Due Date]]=""),"",[@[Due Date]]-TODAY())</f>
+        <f>IF(OR($D9="",$H9=""),"",$H9-TODAY())</f>
         <v/>
       </c>
       <c r="M9" s="17">
-        <f>IF([@[Action Description]]="","",IF(AND([@[Status]]&lt;&gt;"Closed",[@[Status]]&lt;&gt;"Cancelled",[@[Due Date]]&lt;&gt;"",[@[Due Date]]&lt;TODAY()),"Yes","No"))</f>
+        <f>IF($D9="","",IF(AND($I9&lt;&gt;"Closed",$I9&lt;&gt;"Cancelled",$H9&lt;&gt;"",$H9&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
       <c r="N9" s="17">
-        <f t="array" ref="N9">IF([@[Action Description]]="","",IF(IFERROR(MAX(IF(Update_History[Action ID]=[@[Action ID]],ROW(Update_History[Action ID])-7)),0)=0,"",INDEX(Update_History[Update / Discussion],IFERROR(MAX(IF(Update_History[Action ID]=[@[Action ID]],ROW(Update_History[Action ID])-7)),0))))</f>
+        <f t="array" ref="N9">IF($D9="","",IF(IFERROR(MAX(IF(Update_History[Action ID]=$B9,ROW(Update_History[Action ID])-7)),0)=0,"",INDEX(Update_History[Update / Discussion],IFERROR(MAX(IF(Update_History[Action ID]=$B9,ROW(Update_History[Action ID])-7)),0))))</f>
         <v/>
       </c>
       <c r="O9" s="26" t="inlineStr">
@@ -5477,7 +5481,7 @@
         </is>
       </c>
       <c r="X9" s="49">
-        <f>IF([@[Action Description]]="",0,IF(OR([@[Overdue?]]="Yes",[@[Priority]]="Critical"),1,0))</f>
+        <f>IF($D9="",0,IF(OR($M9="Yes",$J9="Critical"),1,0))</f>
         <v/>
       </c>
       <c r="Y9" s="49">
@@ -5515,7 +5519,7 @@
   </conditionalFormatting>
   <dataValidations count="8">
     <dataValidation sqref="C8:C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Topic_Register[Topic ID]</formula1>
+      <formula1>=NAME_TOPIC_IDS</formula1>
     </dataValidation>
     <dataValidation sqref="F8:F9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_ORG</formula1>
@@ -5533,10 +5537,10 @@
       <formula1>=LIST_YESNO</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=PQCP_Follow_Up[PQCP Step]</formula1>
+      <formula1>=NAME_PQCP_STEPS</formula1>
     </dataValidation>
     <dataValidation sqref="S8:S9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Document_Evidence[Evidence ID]</formula1>
+      <formula1>=NAME_EVIDENCE_IDS</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -5737,7 +5741,7 @@
     </row>
     <row r="8">
       <c r="B8">
-        <f>IF([@[Meeting Date]]="","","U"&amp;TEXT(ROW()-7,"0000"))</f>
+        <f>IF($C8="","","U"&amp;TEXT(ROW()-7,"0000"))</f>
         <v/>
       </c>
       <c r="C8" s="27" t="n">
@@ -5788,7 +5792,7 @@
     </row>
     <row r="9">
       <c r="B9">
-        <f>IF([@[Meeting Date]]="","","U"&amp;TEXT(ROW()-7,"0000"))</f>
+        <f>IF($C9="","","U"&amp;TEXT(ROW()-7,"0000"))</f>
         <v/>
       </c>
       <c r="C9" s="27" t="n">
@@ -5854,10 +5858,10 @@
   </mergeCells>
   <dataValidations count="6">
     <dataValidation sqref="D8:D9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Topic_Register[Topic ID]</formula1>
+      <formula1>=NAME_TOPIC_IDS</formula1>
     </dataValidation>
     <dataValidation sqref="E8:E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Action_Register[Action ID]</formula1>
+      <formula1>=NAME_ACTION_IDS</formula1>
     </dataValidation>
     <dataValidation sqref="H8:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_TOPIC_STATUS</formula1>
@@ -6195,7 +6199,7 @@
         </is>
       </c>
       <c r="R8" s="51">
-        <f>IF([@[Readiness Assessment]]="","",IF([@[Readiness Assessment]]="Ready",1,IF([@[Readiness Assessment]]="Partially Ready",0.5,IF([@[Readiness Assessment]]="Not Ready",0,""))))</f>
+        <f>IF($Q8="","",IF($Q8="Ready",1,IF($Q8="Partially Ready",0.5,IF($Q8="Not Ready",0,""))))</f>
         <v/>
       </c>
       <c r="S8" s="26" t="inlineStr">
@@ -6278,7 +6282,7 @@
         </is>
       </c>
       <c r="R9" s="51">
-        <f>IF([@[Readiness Assessment]]="","",IF([@[Readiness Assessment]]="Ready",1,IF([@[Readiness Assessment]]="Partially Ready",0.5,IF([@[Readiness Assessment]]="Not Ready",0,""))))</f>
+        <f>IF($Q9="","",IF($Q9="Ready",1,IF($Q9="Partially Ready",0.5,IF($Q9="Not Ready",0,""))))</f>
         <v/>
       </c>
       <c r="S9" s="26" t="inlineStr">
@@ -6313,13 +6317,13 @@
       <formula1>=LIST_EVIDENCE_AVAIL</formula1>
     </dataValidation>
     <dataValidation sqref="I8:I9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Document_Evidence[Evidence ID]</formula1>
+      <formula1>=NAME_EVIDENCE_IDS</formula1>
     </dataValidation>
     <dataValidation sqref="J8:J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Topic_Register[Topic ID]</formula1>
+      <formula1>=NAME_TOPIC_IDS</formula1>
     </dataValidation>
     <dataValidation sqref="K8:K9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Action_Register[Action ID]</formula1>
+      <formula1>=NAME_ACTION_IDS</formula1>
     </dataValidation>
     <dataValidation sqref="P8:P9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_YESNO</formula1>
@@ -6547,7 +6551,7 @@
     </row>
     <row r="8">
       <c r="B8" s="17">
-        <f>IF([@[Short Description]]="","","E"&amp;TEXT(ROW()-7,"000"))</f>
+        <f>IF($D8="","","E"&amp;TEXT(ROW()-7,"000"))</f>
         <v/>
       </c>
       <c r="C8" s="26" t="inlineStr">
@@ -6619,7 +6623,7 @@
     </row>
     <row r="9">
       <c r="B9" s="17">
-        <f>IF([@[Short Description]]="","","E"&amp;TEXT(ROW()-7,"000"))</f>
+        <f>IF($D9="","","E"&amp;TEXT(ROW()-7,"000"))</f>
         <v/>
       </c>
       <c r="C9" s="26" t="inlineStr">
@@ -6720,13 +6724,13 @@
       <formula1>=LIST_ORG</formula1>
     </dataValidation>
     <dataValidation sqref="K8:K9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Topic_Register[Topic ID]</formula1>
+      <formula1>=NAME_TOPIC_IDS</formula1>
     </dataValidation>
     <dataValidation sqref="L8:L9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Action_Register[Action ID]</formula1>
+      <formula1>=NAME_ACTION_IDS</formula1>
     </dataValidation>
     <dataValidation sqref="M8:M9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=PQCP_Follow_Up[PQCP Step]</formula1>
+      <formula1>=NAME_PQCP_STEPS</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
